--- a/taskbench/data_multimedia/rollback_experiments/recent_experiments_master_table.xlsx
+++ b/taskbench/data_multimedia/rollback_experiments/recent_experiments_master_table.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18353" windowHeight="8880"/>
+    <workbookView windowHeight="13360"/>
   </bookViews>
   <sheets>
     <sheet name="recent_experiments_master_table" sheetId="1" r:id="rId1"/>
@@ -961,7 +961,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -981,6 +981,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1526,7 +1529,9 @@
   <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="14.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="20.9823008849558" customWidth="1"/>
+    <col min="3" max="3" width="55.1150442477876" customWidth="1"/>
+    <col min="25" max="25" width="13.4424778761062" customWidth="1"/>
+    <col min="26" max="26" width="14.5221238938053" customWidth="1"/>
     <col min="30" max="30" width="22.5044247787611" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3816,7 +3821,7 @@
       <c r="Y29" s="6">
         <v>91.35</v>
       </c>
-      <c r="Z29" s="6">
+      <c r="Z29" s="8">
         <v>67.11</v>
       </c>
       <c r="AA29" s="6" t="s">
@@ -3882,7 +3887,7 @@
       <c r="Q30" s="6">
         <v>85.78</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="9">
         <v>65.95</v>
       </c>
       <c r="S30" s="6" t="s">
@@ -3894,7 +3899,7 @@
       <c r="U30" s="6">
         <v>92.23</v>
       </c>
-      <c r="V30" s="8">
+      <c r="V30" s="9">
         <v>71.67</v>
       </c>
       <c r="W30" s="6" t="s">
@@ -3972,7 +3977,7 @@
       <c r="Q31" s="6">
         <v>84.91</v>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="9">
         <v>62.96</v>
       </c>
       <c r="S31" s="6" t="s">
@@ -3984,7 +3989,7 @@
       <c r="U31" s="6">
         <v>92.23</v>
       </c>
-      <c r="V31" s="8">
+      <c r="V31" s="9">
         <v>68.59</v>
       </c>
       <c r="W31" s="6" t="s">
@@ -4072,7 +4077,7 @@
       <c r="Y32" s="6">
         <v>91.6</v>
       </c>
-      <c r="Z32" s="6">
+      <c r="Z32" s="8">
         <v>71.29</v>
       </c>
       <c r="AA32" s="6" t="s">
@@ -4122,7 +4127,7 @@
       <c r="Q33" s="6">
         <v>86.31</v>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="9">
         <v>67.68</v>
       </c>
       <c r="S33" s="6" t="s">
@@ -4134,7 +4139,7 @@
       <c r="U33" s="6">
         <v>92.23</v>
       </c>
-      <c r="V33" s="8">
+      <c r="V33" s="9">
         <v>71.67</v>
       </c>
       <c r="W33" s="6" t="s">
